--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/RHODE_ISLAND_2018.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/RHODE_ISLAND_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C3">
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -460,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -473,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -486,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -499,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -530,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -545,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Total</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -711,12 +811,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C26">
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Total</t>
@@ -812,7 +942,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C33">
@@ -823,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -836,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C35">
@@ -849,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C36">
@@ -862,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -882,7 +1032,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C38">
@@ -893,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -906,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -919,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C41">
@@ -932,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C42">
@@ -945,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -958,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C44">
@@ -971,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C45">
@@ -984,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Florencio Villarreal</t>
@@ -997,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C47">
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -1023,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1036,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -1049,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -1062,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C52">
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -1088,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -1101,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1132,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Atotonilco de Tula</t>
+          <t>Atotonilco De Tula</t>
         </is>
       </c>
       <c r="C57">
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -1210,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1223,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1243,7 +1518,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C65">
@@ -1254,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C66">
@@ -1267,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C67">
@@ -1280,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C68">
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -1306,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1337,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -1350,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1363,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -1376,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1446,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1459,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -1472,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Yecapixtla</t>
@@ -1485,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1516,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Ruíz</t>
@@ -1529,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1560,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -1573,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>San Pedro Mixtepec - Distr. 22 -</t>
@@ -1586,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -1599,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Santo Domingo Tepuxtepec</t>
@@ -1612,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -1625,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1656,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chalchicomula de Sesma</t>
+          <t>Chalchicomula De Sesma</t>
         </is>
       </c>
       <c r="C95">
@@ -1669,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -1682,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C97">
@@ -1695,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1708,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -1721,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -1734,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1747,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1760,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Tepexco</t>
@@ -1773,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Tlacuilotepec</t>
@@ -1786,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -1799,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1819,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C107">
@@ -1830,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C108">
@@ -1843,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1874,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1887,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1900,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1931,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -1944,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1975,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -1988,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2019,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2050,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2063,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -2076,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -2089,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2102,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Tlaltetela</t>
@@ -2115,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Ursulo Galván</t>
@@ -2128,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -2141,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2164,41 +2709,6 @@
       </c>
       <c r="D131">
         <v>1</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
